--- a/AAAGameData/DataTables/Build/DeviceTable.xlsx
+++ b/AAAGameData/DataTables/Build/DeviceTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="51">
   <si>
     <t>#</t>
   </si>
@@ -53,13 +53,19 @@
     <t>PrefabName</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>BuildCapability</t>
+    <t>NameKey</t>
+  </si>
+  <si>
+    <t>DescriptionKey</t>
+  </si>
+  <si>
+    <t>BuildCondition</t>
+  </si>
+  <si>
+    <t>UpgradeID</t>
+  </si>
+  <si>
+    <t>InteractionPanelID</t>
   </si>
   <si>
     <t>int</t>
@@ -96,6 +102,12 @@
     </r>
   </si>
   <si>
+    <t>UnlockCondition</t>
+  </si>
+  <si>
+    <t>enum?</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -120,6 +132,12 @@
     <t>建造条件</t>
   </si>
   <si>
+    <t>升级设备ID</t>
+  </si>
+  <si>
+    <t>交互面板UIViews</t>
+  </si>
+  <si>
     <t>Device_Aaa</t>
   </si>
   <si>
@@ -129,22 +147,25 @@
     <t>Device/Aaa</t>
   </si>
   <si>
-    <t>Item.Material.Name.Aaa</t>
-  </si>
-  <si>
-    <t>Item.Material.Description.Aaa</t>
+    <t>Device.Name.Aaa</t>
+  </si>
+  <si>
+    <t>Device.Description.Aaa</t>
   </si>
   <si>
     <t>Device_Bbb</t>
   </si>
   <si>
+    <t>UIViews.CraftingDialog</t>
+  </si>
+  <si>
     <t>[Material_Aaa, 2],[Material_Bbb, 4]</t>
   </si>
   <si>
-    <t>Item.Material.Name.Bbb</t>
-  </si>
-  <si>
-    <t>Item.Material.Description.Bbb</t>
+    <t>Device.Name.Bbb</t>
+  </si>
+  <si>
+    <t>Device.Description.Bbb</t>
   </si>
   <si>
     <t>Device_Ccc</t>
@@ -153,10 +174,10 @@
     <t>[Material_Aaa, 2],[Material_Bbb, 5]</t>
   </si>
   <si>
-    <t>Item.Material.Name.Ccc</t>
-  </si>
-  <si>
-    <t>Item.Material.Description.Ccc</t>
+    <t>Device.Name.Ccc</t>
+  </si>
+  <si>
+    <t>Device.Description.Ccc</t>
   </si>
   <si>
     <t>Device_Ddd</t>
@@ -165,19 +186,19 @@
     <t>[Material_Aaa, 2],[Material_Bbb, 6],[Material_Ddd, 3]</t>
   </si>
   <si>
-    <t>Item.Material.Name.Ddd</t>
-  </si>
-  <si>
-    <t>Item.Material.Description.Ddd</t>
+    <t>Device.Name.Ddd</t>
+  </si>
+  <si>
+    <t>Device.Description.Ddd</t>
   </si>
   <si>
     <t>Device_Eee</t>
   </si>
   <si>
-    <t>Item.Material.Name.Eee</t>
-  </si>
-  <si>
-    <t>Item.Material.Description.Eee</t>
+    <t>Device.Name.Eee</t>
+  </si>
+  <si>
+    <t>Device.Description.Eee</t>
   </si>
 </sst>
 </file>
@@ -190,14 +211,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -683,137 +697,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
@@ -821,7 +835,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1141,7 +1154,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
@@ -1152,8 +1165,10 @@
     <col min="6" max="7" width="16.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.25" style="1" customWidth="1"/>
     <col min="9" max="9" width="29.5833333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.0833333333333" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.875" style="1"/>
+    <col min="10" max="10" width="14.8333333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.9166666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="20.8333333333333" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1170,7 +1185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="28.75" spans="1:10">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1198,155 +1213,191 @@
       <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="K2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:12">
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="3">
+        <v>31</v>
+      </c>
+      <c r="F5">
         <v>10</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>26</v>
+      <c r="G5" t="s">
+        <v>32</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:9">
+    <row r="6" spans="2:12">
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="3">
+        <v>37</v>
+      </c>
+      <c r="F6">
         <v>15</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>26</v>
+      <c r="G6" t="s">
+        <v>32</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="7" spans="2:9">
+    <row r="7" spans="2:12">
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="3">
+        <v>41</v>
+      </c>
+      <c r="F7">
         <v>20</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>26</v>
+      <c r="G7" t="s">
+        <v>32</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:11">
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="3">
+        <v>45</v>
+      </c>
+      <c r="F8">
         <v>25</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>26</v>
+      <c r="G8" t="s">
+        <v>32</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="2:9">
@@ -1354,22 +1405,22 @@
         <v>5</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" t="s">
         <v>41</v>
       </c>
-      <c r="E9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="F9">
         <v>30</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>26</v>
+      <c r="G9" t="s">
+        <v>32</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
